--- a/output/tabel_evaluasi_klaster.xlsx
+++ b/output/tabel_evaluasi_klaster.xlsx
@@ -463,16 +463,16 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01720863819230496</v>
+        <v>0.01651009383890195</v>
       </c>
       <c r="D2" t="n">
-        <v>6.127359644820022</v>
+        <v>5.395338053395464</v>
       </c>
       <c r="E2" t="n">
-        <v>5.453145547634079</v>
+        <v>7.004844511828352</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9814173211963445</v>
+        <v>0.9762551543062966</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -488,16 +488,16 @@
         <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0.003057286980220535</v>
+        <v>0.01510121285139952</v>
       </c>
       <c r="D3" t="n">
-        <v>4.229303480510594</v>
+        <v>4.453249774379128</v>
       </c>
       <c r="E3" t="n">
-        <v>6.18632163531085</v>
+        <v>8.001976994049144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9586714299093879</v>
+        <v>0.9471823592482663</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -513,16 +513,16 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001104078205206323</v>
+        <v>-0.005759210463438403</v>
       </c>
       <c r="D4" t="n">
-        <v>3.177248601263982</v>
+        <v>3.919501531167347</v>
       </c>
       <c r="E4" t="n">
-        <v>8.893113907571051</v>
+        <v>7.636653434229841</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9146750739088716</v>
+        <v>0.9258361229911756</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
